--- a/parquet - schema/Category.xlsx
+++ b/parquet - schema/Category.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tourism Development Authority</t>
+          <t>Business-Type Activities</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Total Primary Government</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Fund</t>
+          <t>Tourism Development Authority</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>School Improvement Fund</t>
+          <t>Transportation Authority</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other Governmental Funds</t>
+          <t>Total Reporting Unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital Projects Fund</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Opioid Settlement Fund</t>
+          <t>General Fund</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Business-type Activities</t>
+          <t>American Rescue Plan Fund</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Component Units</t>
+          <t>Schools Capital Projects Fund</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Planning Council</t>
+          <t>Other Governmental Funds</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Housing Finance Authority</t>
+          <t>Total Governmental Funds</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Health Facilities Authority</t>
+          <t>Opioid Settlement Fund</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>State Allocation Capital Projects Fund</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital Projects</t>
+          <t>Landfill Fund</t>
         </is>
       </c>
     </row>
@@ -584,197 +584,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emergency Medical Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tourist Development Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>American Rescue Plan Act</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nonmajor Governmental Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Total Governmental Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Water System</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Sewer System</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Solid Waste System</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Total Enterprise Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Governmental Activities - Internal Service Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
           <t>Internal Service Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Shoreline Regional Park Community</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Housing Fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>General Capital Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Park Land Dedication Capital Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Wastewater</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Solid Waste</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Totals</t>
         </is>
       </c>
     </row>
